--- a/Emp Management/Emp Management.xlsx
+++ b/Emp Management/Emp Management.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\donga\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Excel\Excel_Project_Work\Emp Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A5A074-F124-422F-B906-B7B023829DAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90A75C0-1942-444D-BB88-C0EF9E7350D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{7FA3F861-2B47-4A56-99BD-2DE969C49E33}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7FA3F861-2B47-4A56-99BD-2DE969C49E33}"/>
   </bookViews>
   <sheets>
     <sheet name="Student" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="97">
   <si>
     <t>Student ID</t>
   </si>
@@ -224,9 +224,6 @@
     <t>May</t>
   </si>
   <si>
-    <t>Discound Eligible %</t>
-  </si>
-  <si>
     <t xml:space="preserve">Total Sales </t>
   </si>
   <si>
@@ -338,13 +335,25 @@
     <t>Employee Name</t>
   </si>
   <si>
-    <t>Salray (Round)</t>
-  </si>
-  <si>
     <t>Salary (Ceil)</t>
   </si>
   <si>
     <t>Salary (Floor)</t>
+  </si>
+  <si>
+    <t>Average Score Above 60</t>
+  </si>
+  <si>
+    <t>Name (Upper)</t>
+  </si>
+  <si>
+    <t>Name (Lower)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discound Eligible </t>
+  </si>
+  <si>
+    <t>Salary (Round)</t>
   </si>
 </sst>
 </file>
@@ -352,12 +361,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="165" formatCode="[$₹-446]\ #,##0"/>
-    <numFmt numFmtId="166" formatCode="[$₹-447]#,##0"/>
-    <numFmt numFmtId="169" formatCode="dd\-mm\-yyyy"/>
-    <numFmt numFmtId="172" formatCode="[$-14009]dd\-mm\-yyyy;@"/>
-    <numFmt numFmtId="179" formatCode="[$₹-4009]\ #,##0.00"/>
-    <numFmt numFmtId="181" formatCode="[$₹-4009]\ #,##0"/>
+    <numFmt numFmtId="164" formatCode="[$₹-446]\ #,##0"/>
+    <numFmt numFmtId="165" formatCode="[$₹-447]#,##0"/>
+    <numFmt numFmtId="166" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="167" formatCode="[$-14009]dd\-mm\-yyyy;@"/>
+    <numFmt numFmtId="168" formatCode="[$₹-4009]\ #,##0.00"/>
+    <numFmt numFmtId="169" formatCode="[$₹-4009]\ #,##0"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -486,45 +495,43 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -860,24 +867,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E623E00-906D-4AF5-9A87-9B38FC576C1C}">
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.6640625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.77734375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="7" width="8.88671875" style="1"/>
-    <col min="8" max="8" width="12.5546875" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="10.109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.88671875" style="1"/>
-    <col min="16" max="17" width="7.88671875" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="8.88671875" style="1"/>
+    <col min="8" max="9" width="12.5546875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="10.109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.88671875" style="1"/>
+    <col min="19" max="20" width="7.88671875" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -902,23 +911,32 @@
       <c r="H1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J1" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="K1" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>94</v>
+      </c>
       <c r="M1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="N1" s="6">
-        <f>COUNTIF(A1:A10, "&gt;50")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q1" s="6">
+        <f>COUNTIF(D2:D11, "&gt;50")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -946,21 +964,33 @@
         <f>IF(AND(D2&gt;80, E2&gt;80), "YES", "NO")</f>
         <v>YES</v>
       </c>
-      <c r="I2" s="6" t="str">
+      <c r="I2" s="6">
+        <f>IF(AND(D2&gt;60, E2&gt;60), AVERAGE(D2:E2), "-")</f>
+        <v>90</v>
+      </c>
+      <c r="J2" s="6" t="str">
         <f>LEFT(B2, FIND(" ",B2)-1)</f>
         <v>Aarav</v>
       </c>
-      <c r="J2" s="6">
+      <c r="K2" s="6" t="str">
+        <f>UPPER(J2)</f>
+        <v>AARAV</v>
+      </c>
+      <c r="L2" s="6" t="str">
+        <f>LOWER(J2)</f>
+        <v>aarav</v>
+      </c>
+      <c r="M2" s="6">
         <f ca="1">DATEDIF(C2, TODAY(), "y")</f>
         <v>21</v>
       </c>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="10"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="4"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="10"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="4"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" s="6">
         <v>2</v>
       </c>
@@ -988,26 +1018,38 @@
         <f t="shared" ref="H3:H11" si="1">IF(AND(D3&gt;80, E3&gt;80), "YES", "NO")</f>
         <v>NO</v>
       </c>
-      <c r="I3" s="6" t="str">
-        <f t="shared" ref="I3:I11" si="2">LEFT(B3, FIND(" ",B3)-1)</f>
+      <c r="I3" s="6">
+        <f t="shared" ref="I3:I11" si="2">IF(AND(D3&gt;60, E3&gt;60), AVERAGE(D3:E3), "-")</f>
+        <v>78.5</v>
+      </c>
+      <c r="J3" s="6" t="str">
+        <f t="shared" ref="J3:J11" si="3">LEFT(B3, FIND(" ",B3)-1)</f>
         <v>Priya</v>
       </c>
-      <c r="J3" s="6">
-        <f t="shared" ref="J3:J11" ca="1" si="3">DATEDIF(C3, TODAY(), "y")</f>
+      <c r="K3" s="6" t="str">
+        <f t="shared" ref="K3:K11" si="4">UPPER(J3)</f>
+        <v>PRIYA</v>
+      </c>
+      <c r="L3" s="6" t="str">
+        <f t="shared" ref="L3:L11" si="5">LOWER(J3)</f>
+        <v>priya</v>
+      </c>
+      <c r="M3" s="6">
+        <f t="shared" ref="M3:M11" ca="1" si="6">DATEDIF(C3, TODAY(), "y")</f>
         <v>18</v>
       </c>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="5" t="s">
+      <c r="N3" s="4"/>
+      <c r="O3" s="4"/>
+      <c r="P3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="6">
+      <c r="Q3" s="6">
         <v>10</v>
       </c>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="4"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S3" s="13"/>
+      <c r="T3" s="4"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A4" s="6">
         <v>3</v>
       </c>
@@ -1037,24 +1079,36 @@
       </c>
       <c r="I4" s="6" t="str">
         <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+      <c r="J4" s="6" t="str">
+        <f t="shared" si="3"/>
         <v>Rohan</v>
       </c>
-      <c r="J4" s="6">
-        <f t="shared" ca="1" si="3"/>
+      <c r="K4" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>ROHAN</v>
+      </c>
+      <c r="L4" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v>rohan</v>
+      </c>
+      <c r="M4" s="6">
+        <f t="shared" ca="1" si="6"/>
         <v>19</v>
       </c>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="5" t="s">
+      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
+      <c r="P4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="6">
+      <c r="Q4" s="6">
         <v>2</v>
       </c>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="4"/>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S4" s="3"/>
+      <c r="T4" s="4"/>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>4</v>
       </c>
@@ -1082,27 +1136,39 @@
         <f t="shared" si="1"/>
         <v>YES</v>
       </c>
-      <c r="I5" s="6" t="str">
+      <c r="I5" s="6">
         <f t="shared" si="2"/>
+        <v>91</v>
+      </c>
+      <c r="J5" s="6" t="str">
+        <f t="shared" si="3"/>
         <v>Sneha</v>
       </c>
-      <c r="J5" s="6">
-        <f t="shared" ca="1" si="3"/>
+      <c r="K5" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>SNEHA</v>
+      </c>
+      <c r="L5" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v>sneha</v>
+      </c>
+      <c r="M5" s="6">
+        <f t="shared" ca="1" si="6"/>
         <v>18</v>
       </c>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="5" t="s">
+      <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
+      <c r="P5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="12" t="str">
-        <f>VLOOKUP(N3,A2:H11, N4, FALSE)</f>
+      <c r="Q5" s="12" t="str">
+        <f>VLOOKUP(Q3,A2:H11, Q4, FALSE)</f>
         <v>Anaya Reddy</v>
       </c>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="4"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="S5" s="3"/>
+      <c r="T5" s="4"/>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A6" s="6">
         <v>5</v>
       </c>
@@ -1132,20 +1198,32 @@
       </c>
       <c r="I6" s="6" t="str">
         <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+      <c r="J6" s="6" t="str">
+        <f t="shared" si="3"/>
         <v>Karan</v>
       </c>
-      <c r="J6" s="6">
-        <f t="shared" ca="1" si="3"/>
+      <c r="K6" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>KARAN</v>
+      </c>
+      <c r="L6" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v>karan</v>
+      </c>
+      <c r="M6" s="6">
+        <f t="shared" ca="1" si="6"/>
         <v>16</v>
       </c>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
       <c r="N6" s="4"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="14"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O6" s="4"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
+      <c r="S6" s="3"/>
+      <c r="T6" s="14"/>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A7" s="6">
         <v>6</v>
       </c>
@@ -1173,20 +1251,32 @@
         <f t="shared" si="1"/>
         <v>YES</v>
       </c>
-      <c r="I7" s="6" t="str">
+      <c r="I7" s="6">
         <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="J7" s="6" t="str">
+        <f t="shared" si="3"/>
         <v>Diya</v>
       </c>
-      <c r="J7" s="6">
-        <f t="shared" ca="1" si="3"/>
+      <c r="K7" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>DIYA</v>
+      </c>
+      <c r="L7" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v>diya</v>
+      </c>
+      <c r="M7" s="6">
+        <f t="shared" ca="1" si="6"/>
         <v>18</v>
       </c>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
       <c r="N7" s="4"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O7" s="4"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A8" s="6">
         <v>7</v>
       </c>
@@ -1216,18 +1306,30 @@
       </c>
       <c r="I8" s="6" t="str">
         <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+      <c r="J8" s="6" t="str">
+        <f t="shared" si="3"/>
         <v>Arjun</v>
       </c>
-      <c r="J8" s="6">
-        <f t="shared" ca="1" si="3"/>
+      <c r="K8" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>ARJUN</v>
+      </c>
+      <c r="L8" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v>arjun</v>
+      </c>
+      <c r="M8" s="6">
+        <f t="shared" ca="1" si="6"/>
         <v>20</v>
       </c>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
       <c r="N8" s="4"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O8" s="4"/>
+      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>8</v>
       </c>
@@ -1257,18 +1359,30 @@
       </c>
       <c r="I9" s="6" t="str">
         <f t="shared" si="2"/>
+        <v>-</v>
+      </c>
+      <c r="J9" s="6" t="str">
+        <f t="shared" si="3"/>
         <v>Meera</v>
       </c>
-      <c r="J9" s="6">
-        <f t="shared" ca="1" si="3"/>
+      <c r="K9" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>MEERA</v>
+      </c>
+      <c r="L9" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v>meera</v>
+      </c>
+      <c r="M9" s="6">
+        <f t="shared" ca="1" si="6"/>
         <v>18</v>
       </c>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
       <c r="N9" s="4"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O9" s="4"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A10" s="6">
         <v>9</v>
       </c>
@@ -1296,20 +1410,32 @@
         <f t="shared" si="1"/>
         <v>YES</v>
       </c>
-      <c r="I10" s="6" t="str">
+      <c r="I10" s="6">
         <f t="shared" si="2"/>
+        <v>87</v>
+      </c>
+      <c r="J10" s="6" t="str">
+        <f t="shared" si="3"/>
         <v>Vivaan</v>
       </c>
-      <c r="J10" s="6">
-        <f t="shared" ca="1" si="3"/>
+      <c r="K10" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>VIVAAN</v>
+      </c>
+      <c r="L10" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v>vivaan</v>
+      </c>
+      <c r="M10" s="6">
+        <f t="shared" ca="1" si="6"/>
         <v>20</v>
       </c>
-      <c r="K10" s="4"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
       <c r="N10" s="4"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="O10" s="4"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A11" s="6">
         <v>10</v>
       </c>
@@ -1337,23 +1463,35 @@
         <f t="shared" si="1"/>
         <v>NO</v>
       </c>
-      <c r="I11" s="6" t="str">
+      <c r="I11" s="6">
         <f t="shared" si="2"/>
+        <v>69.5</v>
+      </c>
+      <c r="J11" s="6" t="str">
+        <f t="shared" si="3"/>
         <v>Anaya</v>
       </c>
-      <c r="J11" s="6">
-        <f t="shared" ca="1" si="3"/>
+      <c r="K11" s="6" t="str">
+        <f t="shared" si="4"/>
+        <v>ANAYA</v>
+      </c>
+      <c r="L11" s="6" t="str">
+        <f t="shared" si="5"/>
+        <v>anaya</v>
+      </c>
+      <c r="M11" s="6">
+        <f t="shared" ca="1" si="6"/>
         <v>18</v>
       </c>
-      <c r="K11" s="4"/>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
       <c r="N11" s="4"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="N13"/>
-    </row>
-    <row r="14" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="Q13"/>
+    </row>
+    <row r="14" spans="1:20" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
@@ -1364,11 +1502,11 @@
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>1</v>
       </c>
-      <c r="B15" s="6" t="str" cm="1">
+      <c r="B15" s="29" t="str" cm="1">
         <f t="array" ref="B15:B18">_xlfn._xlws.FILTER(B2:B11, (F2:F11&gt;=80))</f>
         <v>Aarav Sharma</v>
       </c>
@@ -1377,7 +1515,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>2</v>
       </c>
@@ -1434,7 +1572,7 @@
     <col min="16" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>26</v>
       </c>
@@ -1463,13 +1601,13 @@
         <v>34</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K1" s="5" t="s">
         <v>35</v>
       </c>
       <c r="L1" s="11" t="s">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="N1" s="3"/>
       <c r="O1" s="3"/>
@@ -1505,14 +1643,14 @@
         <v>165000</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K2" s="6" t="str" cm="1">
         <f t="array" ref="K2">_xlfn.IFS(G2&gt;=50000, "15%", G2&gt;=25000, "10%", G2&gt;=10000, "5%", G2&gt;=5000, "2%", TRUE, "0%")</f>
         <v>15%</v>
       </c>
       <c r="L2" s="6" t="str">
-        <f>IF(G2&gt;=5000, "YES", "NO")</f>
+        <f>IF(OR(G2&gt;=5000,H2&gt;=50),"YES","NO")</f>
         <v>YES</v>
       </c>
       <c r="N2" s="4"/>
@@ -1549,14 +1687,14 @@
         <v>132000</v>
       </c>
       <c r="J3" s="21" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="K3" s="6" t="str" cm="1">
         <f t="array" ref="K3">_xlfn.IFS(G3&gt;=50000, "15%", G3&gt;=25000, "10%", G3&gt;=10000, "5%", G3&gt;=5000, "2%", TRUE, "0%")</f>
         <v>5%</v>
       </c>
       <c r="L3" s="6" t="str">
-        <f t="shared" ref="L3:L11" si="1">IF(G3&gt;=5000, "YES", "NO")</f>
+        <f t="shared" ref="L3:L11" si="1">IF(OR(G3&gt;=5000,H3&gt;=50),"YES","NO")</f>
         <v>YES</v>
       </c>
       <c r="N3" s="4"/>
@@ -1637,7 +1775,7 @@
         <v>48000</v>
       </c>
       <c r="J5" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K5" s="6" t="str" cm="1">
         <f t="array" ref="K5">_xlfn.IFS(G5&gt;=50000, "15%", G5&gt;=25000, "10%", G5&gt;=10000, "5%", G5&gt;=5000, "2%", TRUE, "0%")</f>
@@ -1722,7 +1860,7 @@
         <v>110000</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K7" s="6" t="str" cm="1">
         <f t="array" ref="K7">_xlfn.IFS(G7&gt;=50000, "15%", G7&gt;=25000, "10%", G7&gt;=10000, "5%", G7&gt;=5000, "2%", TRUE, "0%")</f>
@@ -1771,7 +1909,7 @@
       </c>
       <c r="L8" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>NO</v>
+        <v>YES</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
@@ -1804,7 +1942,7 @@
         <v>72000</v>
       </c>
       <c r="J9" s="21" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="K9" s="6" t="str" cm="1">
         <f t="array" ref="K9">_xlfn.IFS(G9&gt;=50000, "15%", G9&gt;=25000, "10%", G9&gt;=10000, "5%", G9&gt;=5000, "2%", TRUE, "0%")</f>
@@ -1845,7 +1983,7 @@
         <v>30000</v>
       </c>
       <c r="J10" s="21" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K10" s="6" t="str" cm="1">
         <f t="array" ref="K10">_xlfn.IFS(G10&gt;=50000, "15%", G10&gt;=25000, "10%", G10&gt;=10000, "5%", G10&gt;=5000, "2%", TRUE, "0%")</f>
@@ -1894,7 +2032,7 @@
       </c>
       <c r="L11" s="6" t="str">
         <f t="shared" si="1"/>
-        <v>NO</v>
+        <v>YES</v>
       </c>
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
@@ -1905,7 +2043,7 @@
         <v>28</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>30</v>
@@ -1914,20 +2052,20 @@
         <v>31</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I14" s="5" t="s">
         <v>28</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K14" s="3"/>
       <c r="M14" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N14" s="5" t="s">
         <v>61</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -1969,7 +2107,7 @@
     </row>
     <row r="17" spans="1:11" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>32</v>
@@ -1978,13 +2116,13 @@
         <v>30</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I17" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J17" s="11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K17" s="18"/>
     </row>
@@ -2004,7 +2142,7 @@
         <v>66000</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J18" s="19">
         <f ca="1">SUM(INDIRECT(I18))</f>
@@ -2044,28 +2182,28 @@
   <sheetData>
     <row r="1" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -2073,26 +2211,26 @@
         <v>1</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D2" s="27">
+        <v>55</v>
+      </c>
+      <c r="D2" s="25">
         <v>62402.7</v>
       </c>
-      <c r="E2" s="26">
+      <c r="E2" s="24">
         <v>43628</v>
       </c>
-      <c r="F2" s="25">
+      <c r="F2" s="28">
         <f>ROUND(D2, 0)</f>
         <v>62403</v>
       </c>
-      <c r="G2" s="25">
+      <c r="G2" s="28">
         <f>_xlfn.CEILING.MATH(D2, 100)</f>
         <v>62500</v>
       </c>
-      <c r="H2" s="24">
+      <c r="H2" s="28">
         <f>_xlfn.FLOOR.MATH(D2, 100)</f>
         <v>62400</v>
       </c>
@@ -2102,24 +2240,28 @@
         <v>2</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="27">
+        <v>83</v>
+      </c>
+      <c r="D3" s="25">
         <v>51354.559999999998</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="24">
         <v>44230</v>
       </c>
-      <c r="F3" s="25">
+      <c r="F3" s="28">
         <f t="shared" ref="F3:F11" si="0">ROUND(D3, 0)</f>
         <v>51355</v>
       </c>
-      <c r="G3" s="25">
+      <c r="G3" s="28">
         <f t="shared" ref="G3:G11" si="1">_xlfn.CEILING.MATH(D3, 100)</f>
         <v>51400</v>
+      </c>
+      <c r="H3" s="28">
+        <f t="shared" ref="H3:H11" si="2">_xlfn.FLOOR.MATH(D3, 100)</f>
+        <v>51300</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -2127,24 +2269,28 @@
         <v>3</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D4" s="27">
+        <v>84</v>
+      </c>
+      <c r="D4" s="25">
         <v>75476.55</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="24">
         <v>43003</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="28">
         <f t="shared" si="0"/>
         <v>75477</v>
       </c>
-      <c r="G4" s="25">
+      <c r="G4" s="28">
         <f t="shared" si="1"/>
         <v>75500</v>
+      </c>
+      <c r="H4" s="28">
+        <f t="shared" si="2"/>
+        <v>75400</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -2152,24 +2298,28 @@
         <v>4</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="27">
+        <v>85</v>
+      </c>
+      <c r="D5" s="25">
         <v>41565.33</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="24">
         <v>44873</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="28">
         <f t="shared" si="0"/>
         <v>41565</v>
       </c>
-      <c r="G5" s="25">
+      <c r="G5" s="28">
         <f t="shared" si="1"/>
         <v>41600</v>
+      </c>
+      <c r="H5" s="28">
+        <f t="shared" si="2"/>
+        <v>41500</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -2177,24 +2327,28 @@
         <v>5</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D6" s="27">
+        <v>86</v>
+      </c>
+      <c r="D6" s="25">
         <v>88363.78</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="24">
         <v>43207</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="28">
         <f t="shared" si="0"/>
         <v>88364</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="28">
         <f t="shared" si="1"/>
         <v>88400</v>
+      </c>
+      <c r="H6" s="28">
+        <f t="shared" si="2"/>
+        <v>88300</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -2202,24 +2356,28 @@
         <v>6</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="27">
+        <v>55</v>
+      </c>
+      <c r="D7" s="25">
         <v>63757.57</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="24">
         <v>44042</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="28">
         <f t="shared" si="0"/>
         <v>63758</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="28">
         <f t="shared" si="1"/>
         <v>63800</v>
+      </c>
+      <c r="H7" s="28">
+        <f t="shared" si="2"/>
+        <v>63700</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -2227,24 +2385,28 @@
         <v>7</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>87</v>
-      </c>
-      <c r="D8" s="27">
+        <v>86</v>
+      </c>
+      <c r="D8" s="25">
         <v>47375.59</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="24">
         <v>44940</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="28">
         <f t="shared" si="0"/>
         <v>47376</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="28">
         <f t="shared" si="1"/>
         <v>47400</v>
+      </c>
+      <c r="H8" s="28">
+        <f t="shared" si="2"/>
+        <v>47300</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -2252,24 +2414,28 @@
         <v>8</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D9" s="27">
+        <v>84</v>
+      </c>
+      <c r="D9" s="25">
         <v>91824.68</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="24">
         <v>42705</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="28">
         <f t="shared" si="0"/>
         <v>91825</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="28">
         <f t="shared" si="1"/>
         <v>91900</v>
+      </c>
+      <c r="H9" s="28">
+        <f t="shared" si="2"/>
+        <v>91800</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -2277,24 +2443,28 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D10" s="25">
+        <v>75235.66</v>
+      </c>
+      <c r="E10" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="D10" s="27">
-        <v>75235.66</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>88</v>
-      </c>
-      <c r="F10" s="25">
+      <c r="F10" s="28">
         <f t="shared" si="0"/>
         <v>75236</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G10" s="28">
         <f t="shared" si="1"/>
         <v>75300</v>
+      </c>
+      <c r="H10" s="28">
+        <f t="shared" si="2"/>
+        <v>75200</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -2302,24 +2472,28 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D11" s="27">
+        <v>55</v>
+      </c>
+      <c r="D11" s="25">
         <v>65175.79</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>89</v>
-      </c>
-      <c r="F11" s="25">
+        <v>88</v>
+      </c>
+      <c r="F11" s="28">
         <f t="shared" si="0"/>
         <v>65176</v>
       </c>
-      <c r="G11" s="25">
+      <c r="G11" s="28">
         <f t="shared" si="1"/>
         <v>65200</v>
+      </c>
+      <c r="H11" s="28">
+        <f t="shared" si="2"/>
+        <v>65100</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
@@ -2331,13 +2505,13 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B13" s="6">
         <v>1</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E13" s="6">
         <v>1</v>
@@ -2345,34 +2519,34 @@
     </row>
     <row r="14" spans="1:8" s="2" customFormat="1" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B14" s="28" t="str">
+        <v>89</v>
+      </c>
+      <c r="B14" s="26" t="str">
         <f>INDEX(B2:B11,MATCH($B$13,A2:A11,0))</f>
         <v>Nikhil Bhatt</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E14" s="29">
+        <v>71</v>
+      </c>
+      <c r="E14" s="27">
         <f>_xlfn.XLOOKUP(E13, A2:A11, D2:D11, "-", 0, 1)</f>
         <v>62402.7</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B15" s="28" t="str">
+        <v>70</v>
+      </c>
+      <c r="B15" s="26" t="str">
         <f>INDEX(C2:C11,MATCH($B$13,A2:A11,0))</f>
         <v>Sales</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="B16" s="29">
+        <v>71</v>
+      </c>
+      <c r="B16" s="27">
         <f>INDEX(D2:D11,MATCH($B$13,A2:A11,0))</f>
         <v>62402.7</v>
       </c>

--- a/Emp Management/Emp Management.xlsx
+++ b/Emp Management/Emp Management.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Excel\Excel_Project_Work\Emp Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F90A75C0-1942-444D-BB88-C0EF9E7350D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF95241-A750-4132-B308-C5B156A46905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7FA3F861-2B47-4A56-99BD-2DE969C49E33}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sales Data" sheetId="2" r:id="rId2"/>
     <sheet name="Employee Data" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>

--- a/Emp Management/Emp Management.xlsx
+++ b/Emp Management/Emp Management.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Excel\Excel_Project_Work\Emp Management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF95241-A750-4132-B308-C5B156A46905}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8CE0720-E7CD-420D-827F-85889478BC20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7FA3F861-2B47-4A56-99BD-2DE969C49E33}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{7FA3F861-2B47-4A56-99BD-2DE969C49E33}"/>
   </bookViews>
   <sheets>
     <sheet name="Student" sheetId="1" r:id="rId1"/>
